--- a/_qa/Duration_Editor_Tests.xlsx
+++ b/_qa/Duration_Editor_Tests.xlsx
@@ -17,6 +17,153 @@
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t>DUR-TRI-011</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Sequential field editing (regression)</t>
+  </si>
+  <si>
+    <t>Triangular distribution selected</t>
+  </si>
+  <si>
+    <t>1. Enter 1 in Left, blur
+2. Enter 5 in Mode, blur
+3. Enter 10 in Right, blur</t>
+  </si>
+  <si>
+    <t>Left and Mode values remain visible after editing Right field</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Regression test for values disappearing bug</t>
+  </si>
+  <si>
+    <t>DUR-TRI-012</t>
+  </si>
+  <si>
+    <t>Values persist across all field changes</t>
+  </si>
+  <si>
+    <t>Triangular with left=1, mode=5, right=10</t>
+  </si>
+  <si>
+    <t>Edit each field in sequence: Left→Mode→Right, blurring after each</t>
+  </si>
+  <si>
+    <t>All three fields retain their values throughout editing</t>
+  </si>
+  <si>
+    <t>Tests direct input state updates in blur handlers</t>
+  </si>
+  <si>
+    <t>DUR-TRI-013</t>
+  </si>
+  <si>
+    <t>Cascade adjustment preserves other values</t>
+  </si>
+  <si>
+    <t>Set left=7 (triggering cascade), then edit right=15</t>
+  </si>
+  <si>
+    <t>After cascade: mode=8, right=9. After right edit: left=7, mode=8, right=15</t>
+  </si>
+  <si>
+    <t>Verifies cascade doesn't clear unrelated fields</t>
+  </si>
+  <si>
+    <t>DUR-UNI-009</t>
+  </si>
+  <si>
+    <t>Uniform distribution selected</t>
+  </si>
+  <si>
+    <t>1. Enter 5 in Low, blur
+2. Enter 15 in High, blur</t>
+  </si>
+  <si>
+    <t>Low value remains visible after editing High field</t>
+  </si>
+  <si>
+    <t>DUR-UNI-010</t>
+  </si>
+  <si>
+    <t>Values persist across field changes</t>
+  </si>
+  <si>
+    <t>Uniform with low=5, high=15</t>
+  </si>
+  <si>
+    <t>Edit Low to 3, blur. Edit High to 20, blur</t>
+  </si>
+  <si>
+    <t>Both fields retain values: Low=3, High=20</t>
+  </si>
+  <si>
+    <t>DUR-UNI-011</t>
+  </si>
+  <si>
+    <t>Cascade adjustment preserves other value</t>
+  </si>
+  <si>
+    <t>Set low=20 (triggering high cascade), then edit high=30</t>
+  </si>
+  <si>
+    <t>After cascade: high=21. After high edit: low=20, high=30</t>
+  </si>
+  <si>
+    <t>Verifies cascade doesn't clear the other field</t>
+  </si>
+  <si>
+    <t>DUR-NORM-009</t>
+  </si>
+  <si>
+    <t>Normal distribution selected</t>
+  </si>
+  <si>
+    <t>1. Enter 10 in Mean, blur
+2. Enter 2 in Std, blur</t>
+  </si>
+  <si>
+    <t>Mean value remains visible after editing Std field</t>
+  </si>
+  <si>
+    <t>DUR-NORM-010</t>
+  </si>
+  <si>
+    <t>Normal with mean=10, std=2</t>
+  </si>
+  <si>
+    <t>Edit Mean to 15, blur. Edit Std to 3, blur</t>
+  </si>
+  <si>
+    <t>Both fields retain values: Mean=15, Std=3</t>
+  </si>
+  <si>
+    <t>DUR-NORM-011</t>
+  </si>
+  <si>
+    <t>Edit both fields with decimals</t>
+  </si>
+  <si>
+    <t>Enter 7.5 in Mean, blur. Enter 1.25 in Std, blur</t>
+  </si>
+  <si>
+    <t>Both decimal values persist: Mean=7.5, Std=1.25</t>
+  </si>
+  <si>
+    <t>Tests decimal handling with sequential edits</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1176,7 +1323,7 @@
     <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,6 +1717,138 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1582,7 +1861,7 @@
     <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,6 +2255,138 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1988,7 +2399,7 @@
     <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,6 +2873,138 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" t="s">
+        <v>6</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_qa/Duration_Editor_Tests.xlsx
+++ b/_qa/Duration_Editor_Tests.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t>DUR-TRI-011</t>
   </si>
@@ -162,6 +162,1642 @@
   </si>
   <si>
     <t>Tests decimal handling with sequential edits</t>
+  </si>
+  <si>
+    <t>DUR-EXP-001</t>
+  </si>
+  <si>
+    <t>Enter valid scale value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected that uses a Duration Editor
+2. Find the Duration section in the editor panel
+3. Click the distribution type dropdown (it shows current type)
+4. Select "Exponential" from the dropdown list
+5. The Scale field should now be visible</t>
+  </si>
+  <si>
+    <t>1. Find the "Scale" number field
+   (Scale = mean time between events in exponential distribution)
+2. Click inside the Scale field
+3. Clear any existing value
+4. Type "1.5"
+5. Press Tab or click outside the field (this is called "blur")</t>
+  </si>
+  <si>
+    <t>1. The Scale field now displays "1.5"
+2. The value is accepted without errors
+3. The parent form's Save button should become enabled (blue)
+4. The scale value represents the average duration
+5. Example: Scale of 1.5 means average duration is 1.5 time units</t>
+  </si>
+  <si>
+    <t>DUR-EXP-002</t>
+  </si>
+  <si>
+    <t>Enter decimal value like 0.25</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field is visible and accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear any existing value
+3. Type "0.25" (a decimal less than 1)
+4. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Scale field accepts the decimal value
+2. The field displays "0.25"
+3. Small scale values are valid for fast exponential processes
+4. No error messages appear
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>DUR-EXP-003</t>
+  </si>
+  <si>
+    <t>Enter value below minimum (zero)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field currently shows a valid value (like 1)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear the existing value
+3. Type "0" (zero)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the field value</t>
+  </si>
+  <si>
+    <t>1. The field should NOT keep the value 0
+2. The value should automatically change to the minimum allowed (0.01)
+3. This is because exponential scale must be positive
+4. Zero or negative scale doesn't make sense mathematically
+5. The minimum enforcement happens on blur (losing focus)</t>
+  </si>
+  <si>
+    <t>DUR-EXP-004</t>
+  </si>
+  <si>
+    <t>Clear field completely and blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field shows a valid value (like 1.5)</t>
+  </si>
+  <si>
+    <t>1. Note the current Scale value (e.g., "1.5")
+2. Click inside the Scale field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value (e.g., "1.5")
+3. This prevents accidentally leaving the field blank
+4. Empty values are not valid for exponential scale
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-EXP-005</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Use spinner up arrow to increase value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field shows value "1"
+4. Look for small up/down arrow buttons on the Scale field</t>
+  </si>
+  <si>
+    <t>1. Find the Scale field with spinner arrows (▲▼ buttons)
+2. Make sure the current value is "1"
+3. Click the UP arrow (▲) once
+4. Observe how the value changes
+5. Note the increment amount</t>
+  </si>
+  <si>
+    <t>1. The Scale value increases by a small step amount
+2. The step is typically 0.01 or 0.1 (note the actual step)
+3. If value was 1, it might become 1.01 or 1.1
+4. The Save button becomes enabled
+5. This provides an alternative to typing values</t>
+  </si>
+  <si>
+    <t>DUR-EXP-006</t>
+  </si>
+  <si>
+    <t>Use spinner down arrow to decrease value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field shows value "1"
+4. Spinner arrows (▲▼) are visible on the field</t>
+  </si>
+  <si>
+    <t>1. Find the Scale field with spinner arrows
+2. Make sure the current value is "1"
+3. Click the DOWN arrow (▼) multiple times
+4. Keep clicking until the value gets very small
+5. Observe if there's a minimum it won't go below</t>
+  </si>
+  <si>
+    <t>1. The Scale value decreases by a small step each click
+2. The value should stop decreasing at the minimum (0.01)
+3. The spinner should NOT allow going to 0 or negative
+4. This protects against invalid exponential parameters
+5. Note: The minimum is enforced even with spinner controls</t>
+  </si>
+  <si>
+    <t>DUR-EXP-007</t>
+  </si>
+  <si>
+    <t>Enter negative value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field shows a valid positive value</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear the existing value
+3. Type "-1" (negative one)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the negative value</t>
+  </si>
+  <si>
+    <t>1. The field should NOT accept the negative value
+2. The value should automatically change to the minimum (0.01)
+3. Exponential distribution requires positive scale values
+4. Negative scale is mathematically invalid
+5. The correction happens on blur (losing focus)</t>
+  </si>
+  <si>
+    <t>DUR-EXP-008</t>
+  </si>
+  <si>
+    <t>Enter very large value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Exponential distribution selected
+3. The Scale field is visible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear any existing value
+3. Type "10000" (a large number)
+4. Press Tab or click outside the field
+5. Check if the value is accepted</t>
+  </si>
+  <si>
+    <t>1. The Scale field should accept the large value
+2. The field displays "10000"
+3. No error messages appear
+4. Large scale values are valid (means long average duration)
+5. Note: Very large values may affect simulation performance</t>
+  </si>
+  <si>
+    <t>DUR-CONST-001</t>
+  </si>
+  <si>
+    <t>Enter positive value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected that uses a Duration Editor
+2. Find the Duration section in the editor panel
+3. Click the distribution type dropdown
+4. Select "Constant" from the dropdown list
+5. The Value field should now be visible
+   (Constant means every duration is exactly the same)</t>
+  </si>
+  <si>
+    <t>1. Find the "Value" number field
+   (This is the fixed duration that will be used every time)
+2. Click inside the Value field
+3. Clear any existing value
+4. Type "10"
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Value field now displays "10"
+2. The value is accepted without errors
+3. The parent form's Save button becomes enabled (blue)
+4. This means every duration will be exactly 10 time units
+5. Constant distribution = no randomness, always same value</t>
+  </si>
+  <si>
+    <t>DUR-CONST-002</t>
+  </si>
+  <si>
+    <t>Enter zero value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Constant distribution selected
+3. The Value field is visible and accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Value field
+2. Clear any existing value
+3. Type "0" (zero)
+4. Press Tab or click outside the field
+5. Observe if zero is accepted</t>
+  </si>
+  <si>
+    <t>1. The Value field should accept 0
+2. The field displays "0"
+3. Zero duration means instant/no delay
+4. This is valid for some simulation scenarios
+5. Note: Check if the application allows zero or enforces a minimum</t>
+  </si>
+  <si>
+    <t>DUR-CONST-003</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Constant distribution selected
+3. The Value field shows a positive value</t>
+  </si>
+  <si>
+    <t>1. Click inside the Value field
+2. Clear the existing value
+3. Type "-5" (negative five)
+4. Press Tab or click outside the field
+5. Watch what happens to the negative value</t>
+  </si>
+  <si>
+    <t>1. Check how the application handles negative duration
+2. Possible behaviors:
+   - Accepts -5 (some simulations allow negative for special cases)
+   - Rejects and reverts to 0 or minimum
+   - Shows an error message
+3. Document the actual behavior you observe
+4. Negative durations may or may not make sense depending on context</t>
+  </si>
+  <si>
+    <t>DUR-CONST-004</t>
+  </si>
+  <si>
+    <t>Enter decimal value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Constant distribution selected
+3. The Value field is visible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Value field
+2. Clear any existing value
+3. Type "2.5" (a decimal value)
+4. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Value field accepts the decimal value
+2. The field displays "2.5"
+3. Decimal durations are valid (e.g., 2.5 minutes)
+4. No error messages appear
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>DUR-CONST-005</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Constant distribution selected
+3. The Value field shows a valid value (like 10)</t>
+  </si>
+  <si>
+    <t>1. Note the current Value (e.g., "10")
+2. Click inside the Value field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value (e.g., "10")
+3. This prevents accidentally leaving the field blank
+4. Empty values are not valid for constant duration
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-CONST-006</t>
+  </si>
+  <si>
+    <t>Use spinner controls to adjust value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Constant distribution selected
+3. The Value field shows "5"
+4. Look for small up/down arrow buttons on the Value field</t>
+  </si>
+  <si>
+    <t>1. Find the Value field with spinner arrows (▲▼ buttons)
+2. Make sure the current value is "5"
+3. Click the UP arrow (▲) once - note the new value
+4. Click the DOWN arrow (▼) twice - note the new value
+5. Observe the step increment amount</t>
+  </si>
+  <si>
+    <t>1. UP arrow increases the value by a step amount
+2. DOWN arrow decreases the value by a step amount
+3. The step is typically a small number (0.01, 0.1, or 1)
+4. The spinner provides quick value adjustment
+5. Check if there's a minimum the DOWN arrow won't go below</t>
+  </si>
+  <si>
+    <t>DUR-NORM-001</t>
+  </si>
+  <si>
+    <t>Enter valid mean value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected that uses a Duration Editor
+2. Find the Duration section in the editor panel
+3. Click the distribution type dropdown
+4. Select "Normal" from the dropdown list
+5. Two fields should now be visible: "Mean" and "Std" (Standard Deviation)</t>
+  </si>
+  <si>
+    <t>1. Find the "Mean" number field
+   (Mean = average duration, center of the bell curve)
+2. Click inside the Mean field
+3. Clear any existing value
+4. Type "10"
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Mean field now displays "10"
+2. The value is accepted without errors
+3. The parent form's Save button becomes enabled (blue)
+4. Mean of 10 means average duration is 10 time units
+5. Actual durations will vary around this mean based on Std</t>
+  </si>
+  <si>
+    <t>DUR-NORM-002</t>
+  </si>
+  <si>
+    <t>Enter valid standard deviation value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. Both Mean and Std fields are visible
+4. Mean already has a value</t>
+  </si>
+  <si>
+    <t>1. Find the "Std" (Standard Deviation) number field
+   (Std = how spread out the durations are from the mean)
+2. Click inside the Std field
+3. Clear any existing value
+4. Type "2"
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Std field now displays "2"
+2. The value is accepted without errors
+3. Std of 2 means most durations fall within Mean ± 2 (i.e., 8-12)
+4. Larger Std = more variation in duration
+5. Smaller Std = durations cluster tightly around mean</t>
+  </si>
+  <si>
+    <t>DUR-NORM-003</t>
+  </si>
+  <si>
+    <t>Enter negative mean value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. The Mean field shows a positive value</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mean field
+2. Clear the existing value
+3. Type "-5" (negative five)
+4. Press Tab or click outside the field
+5. Watch what happens</t>
+  </si>
+  <si>
+    <t>1. The Mean field should accept -5
+2. The field displays "-5"
+3. Negative mean IS mathematically valid for normal distribution
+4. This could represent things like delays vs advances
+5. Note: May cause negative durations in simulation (check app behavior)</t>
+  </si>
+  <si>
+    <t>DUR-NORM-004</t>
+  </si>
+  <si>
+    <t>Enter zero in standard deviation field</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. The Std field shows a positive value (like 2)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Std field
+2. Clear the existing value
+3. Type "0" (zero)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the zero value</t>
+  </si>
+  <si>
+    <t>1. The field should NOT accept 0 for standard deviation
+2. The value should automatically change to minimum (0.1)
+3. Zero Std would mean no variation (use Constant instead)
+4. Standard deviation must be positive for normal distribution
+5. The minimum is enforced on blur</t>
+  </si>
+  <si>
+    <t>DUR-NORM-005</t>
+  </si>
+  <si>
+    <t>Enter negative standard deviation</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. The Std field shows a positive value</t>
+  </si>
+  <si>
+    <t>1. Click inside the Std field
+2. Clear the existing value
+3. Type "-1" (negative one)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the negative value</t>
+  </si>
+  <si>
+    <t>1. The field should NOT accept negative Std
+2. The value should automatically change to minimum (0.1)
+3. Standard deviation cannot be negative (mathematically invalid)
+4. The correction happens on blur
+5. Only positive Std values make sense</t>
+  </si>
+  <si>
+    <t>DUR-NORM-006</t>
+  </si>
+  <si>
+    <t>Clear mean field and blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. The Mean field shows "10"</t>
+  </si>
+  <si>
+    <t>1. Note the current Mean value ("10")
+2. Click inside the Mean field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("10")
+3. This prevents accidentally leaving the field blank
+4. Empty values are not valid for distribution parameters
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-NORM-007</t>
+  </si>
+  <si>
+    <t>Clear std field and blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. The Std field shows "2"</t>
+  </si>
+  <si>
+    <t>1. Note the current Std value ("2")
+2. Click inside the Std field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside the field ("blur")
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("2")
+3. This prevents accidentally leaving the field blank
+4. Standard deviation cannot be empty
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-NORM-008</t>
+  </si>
+  <si>
+    <t>Enter decimal values in both fields</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. Both Mean and Std fields are accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mean field
+2. Clear and type "5.5" (decimal mean)
+3. Press Tab to move to Std field
+4. Clear and type "1.25" (decimal std)
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Mean field displays "5.5"
+2. Std field displays "1.25"
+3. Both decimal values are accepted
+4. Decimal parameters are valid for normal distribution
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>Sequential field editing (regression test)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. Both fields may have default or existing values
+4. This tests a bug where editing one field erased another</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mean field
+2. Clear and type "10"
+3. Press Tab to move to Std field (blur Mean)
+4. Type "2" in the Std field
+5. Press Tab to blur Std field
+6. Look back at the Mean field</t>
+  </si>
+  <si>
+    <t>1. CRITICAL: The Mean field still shows "10" (not blank!)
+2. The Std field shows "2"
+3. Editing Std did NOT erase the Mean value
+4. This is a regression test for a previous bug
+5. Both values should persist after sequential editing</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. Mean is "10", Std is "2"</t>
+  </si>
+  <si>
+    <t>1. Change Mean from "10" to "15", then blur (Tab or click out)
+2. Verify Mean shows "15"
+3. Change Std from "2" to "3", then blur
+4. Verify Std shows "3"
+5. Check that Mean still shows "15"</t>
+  </si>
+  <si>
+    <t>1. After changing Mean: Mean=15, Std unchanged
+2. After changing Std: Std=3, Mean still=15
+3. Both values persist correctly
+4. No field loses its value when editing the other
+5. This tests the blur handler state updates work correctly</t>
+  </si>
+  <si>
+    <t>Edit both fields with decimal values</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with Normal distribution selected
+3. Fields have some initial values</t>
+  </si>
+  <si>
+    <t>1. Click Mean field, clear, type "7.5", then blur
+2. Click Std field, clear, type "1.25", then blur
+3. Click back on Mean field (don't change, just check value)
+4. Click back on Std field (don't change, just check value)</t>
+  </si>
+  <si>
+    <t>1. Mean field shows "7.5" throughout all steps
+2. Std field shows "1.25" throughout all steps
+3. Decimal values persist correctly across sequential edits
+4. Clicking fields doesn't reset or lose values
+5. This tests decimal handling with sequential edits</t>
+  </si>
+  <si>
+    <t>DUR-UNI-001</t>
+  </si>
+  <si>
+    <t>Enter valid low and high values</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected that uses a Duration Editor
+2. Find the Duration section in the editor panel
+3. Click the distribution type dropdown
+4. Select "Uniform" from the dropdown list
+5. Two fields should appear: "Low" and "High"</t>
+  </si>
+  <si>
+    <t>1. Find the "Low" field (minimum duration)
+2. Click inside Low field, clear, type "5"
+3. Press Tab to move to "High" field
+4. Click inside High field, clear, type "15"
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Low field displays "5"
+2. High field displays "15"
+3. Both values are accepted
+4. Uniform distribution will randomly pick values between 5 and 15
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>DUR-UNI-002</t>
+  </si>
+  <si>
+    <t>Set low equal to high (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Uniform distribution selected
+3. Low is "5", High is "15"</t>
+  </si>
+  <si>
+    <t>1. Click inside the Low field
+2. Clear and type "15" (same as current High)
+3. Press Tab or click outside to blur
+4. Watch what happens to the High value</t>
+  </si>
+  <si>
+    <t>1. Low field shows "15"
+2. IMPORTANT: High field AUTO-ADJUSTS to "15.01"
+3. This is cascade adjustment - High must be &gt; Low
+4. The system ensures Low &lt; High automatically
+5. Uniform distribution requires a range (can't have low = high)</t>
+  </si>
+  <si>
+    <t>DUR-UNI-003</t>
+  </si>
+  <si>
+    <t>Set low greater than high (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Low field
+2. Clear and type "20" (greater than current High of 15)
+3. Press Tab or click outside to blur
+4. Watch what happens to the High value</t>
+  </si>
+  <si>
+    <t>1. Low field shows "20"
+2. IMPORTANT: High field AUTO-ADJUSTS to "20.01"
+3. The system maintains the rule: High &gt; Low
+4. Setting Low above High triggers cascade adjustment
+5. This prevents invalid uniform distribution parameters</t>
+  </si>
+  <si>
+    <t>DUR-UNI-004</t>
+  </si>
+  <si>
+    <t>Set high equal to low (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the High field
+2. Clear and type "5" (same as current Low)
+3. Press Tab or click outside to blur
+4. Watch what happens to the Low value</t>
+  </si>
+  <si>
+    <t>1. High field shows "5"
+2. IMPORTANT: Low field AUTO-ADJUSTS to "4.99"
+3. This is cascade adjustment - Low must be &lt; High
+4. The system ensures Low &lt; High automatically
+5. Uniform distribution requires a range (can't have high = low)</t>
+  </si>
+  <si>
+    <t>DUR-UNI-005</t>
+  </si>
+  <si>
+    <t>Set high less than low (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the High field
+2. Clear and type "2" (less than current Low of 5)
+3. Press Tab or click outside to blur
+4. Watch what happens to the Low value</t>
+  </si>
+  <si>
+    <t>1. High field shows "2"
+2. IMPORTANT: Low field AUTO-ADJUSTS to "1.99"
+3. The system maintains the rule: Low &lt; High
+4. Setting High below Low triggers cascade adjustment
+5. This prevents invalid uniform distribution parameters</t>
+  </si>
+  <si>
+    <t>DUR-UNI-006</t>
+  </si>
+  <si>
+    <t>Enter decimal values</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Uniform distribution selected
+3. Both Low and High fields are accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside Low field, clear, type "0.5"
+2. Press Tab to move to High field
+3. Clear and type "2.75"
+4. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Low field displays "0.5"
+2. High field displays "2.75"
+3. Decimal values are accepted
+4. Uniform will pick random values between 0.5 and 2.75
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>DUR-UNI-007</t>
+  </si>
+  <si>
+    <t>Clear low field and blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Uniform distribution selected
+3. Low shows "5", High shows "15"</t>
+  </si>
+  <si>
+    <t>1. Note the current Low value ("5")
+2. Click inside the Low field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside to blur
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("5")
+3. This prevents accidentally leaving the field blank
+4. Empty values are not valid for distribution parameters
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-UNI-008</t>
+  </si>
+  <si>
+    <t>Clear high field and blur</t>
+  </si>
+  <si>
+    <t>1. Note the current High value ("15")
+2. Click inside the High field
+3. Select all text and DELETE it (field is now empty)
+4. Press Tab or click outside to blur
+5. Watch what happens to the empty field</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("15")
+3. This prevents accidentally leaving the field blank
+4. Empty values are not valid for distribution parameters
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Uniform distribution selected
+3. Both fields may have default or existing values
+4. This tests a bug where editing one field erased another</t>
+  </si>
+  <si>
+    <t>1. Click inside the Low field
+2. Clear and type "5"
+3. Press Tab to move to High field (blur Low)
+4. Type "15" in the High field
+5. Press Tab to blur High field
+6. Look back at the Low field</t>
+  </si>
+  <si>
+    <t>1. CRITICAL: The Low field still shows "5" (not blank!)
+2. The High field shows "15"
+3. Editing High did NOT erase the Low value
+4. This is a regression test for a previous bug
+5. Both values should persist after sequential editing</t>
+  </si>
+  <si>
+    <t>1. Change Low from "5" to "3", then blur
+2. Verify Low shows "3"
+3. Change High from "15" to "20", then blur
+4. Verify High shows "20"
+5. Check that Low still shows "3"</t>
+  </si>
+  <si>
+    <t>1. After changing Low: Low=3, High unchanged at 15
+2. After changing High: High=20, Low still=3
+3. Both values persist correctly
+4. No field loses its value when editing the other
+5. This tests the blur handler state updates work correctly</t>
+  </si>
+  <si>
+    <t>1. Set Low to "20" (triggers High cascade to 20.01)
+2. Now edit High to "30"
+3. Press Tab to blur
+4. Check both field values</t>
+  </si>
+  <si>
+    <t>1. After Low=20 cascade: Low=20, High=20.01 (auto-adjusted)
+2. After editing High to 30: Low=20, High=30
+3. The cascade did NOT reset or clear the Low field
+4. Editing High after cascade works correctly
+5. This verifies cascade doesn't break subsequent edits</t>
+  </si>
+  <si>
+    <t>DUR-TRI-001</t>
+  </si>
+  <si>
+    <t>Enter valid left/mode/right values</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected that uses a Duration Editor
+2. Find the Duration section in the editor panel
+3. Click the distribution type dropdown
+4. Select "Triangular" from the dropdown list
+5. Three fields should appear: "Left", "Mode", "Right"</t>
+  </si>
+  <si>
+    <t>1. Find the three fields:
+   - Left = minimum possible duration
+   - Mode = most likely duration (peak of triangle)
+   - Right = maximum possible duration
+2. Click Left, clear, type "1", blur
+3. Click Mode, clear, type "5", blur
+4. Click Right, clear, type "10", blur</t>
+  </si>
+  <si>
+    <t>1. Left shows "1", Mode shows "5", Right shows "10"
+2. All values are accepted
+3. Rule: Left ≤ Mode ≤ Right must be maintained
+4. Most durations will be around the Mode (5)
+5. The Save button becomes enabled</t>
+  </si>
+  <si>
+    <t>DUR-TRI-002</t>
+  </si>
+  <si>
+    <t>Set left greater than mode (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Triangular selected
+3. Left="1", Mode="5", Right="10"</t>
+  </si>
+  <si>
+    <t>1. Click inside the Left field
+2. Clear and type "7" (greater than Mode of 5)
+3. Press Tab or click outside to blur
+4. Watch what happens to Mode and Right</t>
+  </si>
+  <si>
+    <t>1. Left field shows "7"
+2. IMPORTANT: Mode AUTO-ADJUSTS to "8" (must be &gt; Left)
+3. IMPORTANT: Right AUTO-ADJUSTS to "9" (must be &gt; Mode)
+4. This is cascade adjustment - maintains Left &lt; Mode &lt; Right
+5. The system prevents invalid triangular parameters</t>
+  </si>
+  <si>
+    <t>DUR-TRI-003</t>
+  </si>
+  <si>
+    <t>Set right less than mode (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Right field
+2. Clear and type "3" (less than Mode of 5)
+3. Press Tab or click outside to blur
+4. Watch what happens to Mode and Left</t>
+  </si>
+  <si>
+    <t>1. Right field shows "3"
+2. IMPORTANT: Mode AUTO-ADJUSTS to "2" (must be &lt; Right)
+3. IMPORTANT: Left AUTO-ADJUSTS to "1" (must be &lt; Mode)
+4. This is cascade adjustment - maintains Left &lt; Mode &lt; Right
+5. The system prevents invalid triangular parameters</t>
+  </si>
+  <si>
+    <t>DUR-TRI-004</t>
+  </si>
+  <si>
+    <t>Set mode below left (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mode field
+2. Clear and type "0" (less than Left of 1)
+3. Press Tab or click outside to blur
+4. Watch what happens to Left</t>
+  </si>
+  <si>
+    <t>1. Mode field shows "0"
+2. IMPORTANT: Left AUTO-ADJUSTS to "-0.01" or minimum
+3. This maintains Left &lt; Mode rule
+4. If negative isn't allowed, check the actual adjusted value
+5. The cascade ensures valid triangular distribution</t>
+  </si>
+  <si>
+    <t>DUR-TRI-005</t>
+  </si>
+  <si>
+    <t>Set mode above right (cascade adjustment)</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mode field
+2. Clear and type "15" (greater than Right of 10)
+3. Press Tab or click outside to blur
+4. Watch what happens to Right</t>
+  </si>
+  <si>
+    <t>1. Mode field shows "15"
+2. IMPORTANT: Right AUTO-ADJUSTS to "15.01" or higher
+3. This maintains Mode &lt; Right rule
+4. The cascade ensures valid triangular distribution
+5. Left remains unchanged (still valid)</t>
+  </si>
+  <si>
+    <t>DUR-TRI-006</t>
+  </si>
+  <si>
+    <t>Enter decimal values in all fields</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Triangular selected
+3. All three fields are accessible</t>
+  </si>
+  <si>
+    <t>1. Click Left, clear, type "0.5", blur
+2. Click Mode, clear, type "1.75", blur
+3. Click Right, clear, type "3.25", blur</t>
+  </si>
+  <si>
+    <t>1. Left shows "0.5"
+2. Mode shows "1.75"
+3. Right shows "3.25"
+4. All decimal values are accepted
+5. Rule maintained: 0.5 &lt; 1.75 &lt; 3.25</t>
+  </si>
+  <si>
+    <t>DUR-TRI-007</t>
+  </si>
+  <si>
+    <t>Set all three values equal (spread enforced)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Triangular selected
+3. Fields have some valid values</t>
+  </si>
+  <si>
+    <t>1. Try to set Left="5", Mode="5", Right="5"
+2. Set Left to 5, blur
+3. Set Mode to 5, blur (watch cascade)
+4. Set Right to 5, blur (watch cascade)
+5. Observe final values</t>
+  </si>
+  <si>
+    <t>1. The system should enforce minimum spread
+2. Left, Mode, Right cannot all be exactly equal
+3. Cascade adjustments will create small differences
+4. Example final values: Left=4.98, Mode=4.99, Right=5
+5. This ensures a valid triangular distribution</t>
+  </si>
+  <si>
+    <t>DUR-TRI-008</t>
+  </si>
+  <si>
+    <t>Clear left field and blur</t>
+  </si>
+  <si>
+    <t>1. Note current Left value ("1")
+2. Click inside the Left field
+3. Select all and DELETE (field is empty)
+4. Press Tab or click outside to blur
+5. Watch what happens</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("1")
+3. This prevents accidentally leaving required fields blank
+4. Empty values are invalid for triangular distribution
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-TRI-009</t>
+  </si>
+  <si>
+    <t>Clear mode field and blur</t>
+  </si>
+  <si>
+    <t>1. Note current Mode value ("5")
+2. Click inside the Mode field
+3. Select all and DELETE (field is empty)
+4. Press Tab or click outside to blur
+5. Watch what happens</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("5")
+3. This prevents accidentally leaving required fields blank
+4. Mode is the most important triangular parameter
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>DUR-TRI-010</t>
+  </si>
+  <si>
+    <t>Clear right field and blur</t>
+  </si>
+  <si>
+    <t>1. Note current Right value ("10")
+2. Click inside the Right field
+3. Select all and DELETE (field is empty)
+4. Press Tab or click outside to blur
+5. Watch what happens</t>
+  </si>
+  <si>
+    <t>1. The field should NOT remain empty
+2. It should revert to the PREVIOUS valid value ("10")
+3. This prevents accidentally leaving required fields blank
+4. Empty values are invalid for triangular distribution
+5. The revert happens automatically on blur</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor with Triangular selected
+3. Fields may have default or existing values
+4. This tests a bug where editing one field erased others</t>
+  </si>
+  <si>
+    <t>1. Click Left field, clear, type "1", blur
+2. Click Mode field, clear, type "5", blur
+3. Click Right field, clear, type "10", blur
+4. Look back at Left and Mode fields</t>
+  </si>
+  <si>
+    <t>1. CRITICAL: Left still shows "1" (not blank!)
+2. CRITICAL: Mode still shows "5" (not blank!)
+3. Right shows "10"
+4. No field was erased by editing other fields
+5. This is a regression test for a previous bug</t>
+  </si>
+  <si>
+    <t>1. Change Left to "2", blur, verify Left=2
+2. Change Mode to "6", blur, verify Mode=6, Left still=2
+3. Change Right to "12", blur, verify Right=12
+4. Verify final state: Left=2, Mode=6, Right=12</t>
+  </si>
+  <si>
+    <t>1. Each field change persists correctly
+2. Editing one field does NOT erase others
+3. Final state: Left=2, Mode=6, Right=12
+4. All three values maintained correctly
+5. This tests blur handler state updates work for 3 fields</t>
+  </si>
+  <si>
+    <t>1. Set Left to "7" (triggers cascade on Mode and Right)
+2. After cascade completes, edit Right to "15"
+3. Press Tab to blur
+4. Check all three field values</t>
+  </si>
+  <si>
+    <t>1. After Left=7 cascade: Mode~8, Right~9 (auto-adjusted)
+2. After editing Right to 15: Left=7, Mode=8, Right=15
+3. The cascade did NOT reset Left to a different value
+4. Subsequent edits work correctly after cascade
+5. This verifies cascade doesn't break state management</t>
+  </si>
+  <si>
+    <t>DUR-DEC-001</t>
+  </si>
+  <si>
+    <t>Type .25 starting with decimal point</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Exponential" distribution from dropdown
+4. The Scale field is visible
+5. This tests typing decimals starting with a dot</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear any existing value
+3. Type ".25" (starting with the decimal point, no leading zero)
+4. Watch the field as you type each character
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. While typing, the field should show "." then ".2" then ".25"
+2. After blur, field shows either ".25" or "0.25"
+3. The decimal value is accepted without errors
+4. This is a REGRESSION TEST for a previous decimal input bug
+5. The value should NOT reset or disappear while typing</t>
+  </si>
+  <si>
+    <t>DUR-DEC-002</t>
+  </si>
+  <si>
+    <t>Type 0.25 with leading zero</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Exponential" distribution
+4. The Scale field is visible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear any existing value
+3. Type "0.25" character by character: 0, ., 2, 5
+4. Watch the field display after each keystroke
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Field should progressively show: "0", "0.", "0.2", "0.25"
+2. The value should NOT jump or reset during typing
+3. After blur, field shows "0.25"
+4. The decimal was handled smoothly
+5. This tests standard decimal input behavior</t>
+  </si>
+  <si>
+    <t>DUR-DEC-003</t>
+  </si>
+  <si>
+    <t>Type 0. then 2 then 5 (progressive decimal)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Exponential" distribution
+4. The Scale field is visible
+5. KEY TEST for decimal typing fix</t>
+  </si>
+  <si>
+    <t>1. Click inside the Scale field
+2. Clear any existing value
+3. Type "0" - pause and check field shows "0"
+4. Type "." - pause and check field shows "0."
+5. Type "2" - check field shows "0.2"
+6. Type "5" - check field shows "0.25"
+7. Blur the field</t>
+  </si>
+  <si>
+    <t>1. CRITICAL: Field should show intermediate values:
+   - After "0": shows "0"
+   - After ".": shows "0." (not reset!)
+   - After "2": shows "0.2"
+   - After "5": shows "0.25"
+2. The decimal point should NOT cause field to clear
+3. This is the KEY regression test for decimal typing
+4. Previous bug: typing "." would erase the field</t>
+  </si>
+  <si>
+    <t>DUR-DEC-004</t>
+  </si>
+  <si>
+    <t>Type decimal in Normal mean field</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Normal" distribution
+4. Mean and Std fields are visible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Mean field
+2. Clear any existing value
+3. Type "0.5" character by character
+4. Watch the field during typing
+5. Press Tab to move to Std field</t>
+  </si>
+  <si>
+    <t>1. Field progressively shows: "0", "0.", "0.5"
+2. Decimal is handled correctly in Mean field
+3. After Tab, Mean shows "0.5" and cursor moves to Std
+4. The value persists (doesn't reset)
+5. Normal distribution accepts decimal mean values</t>
+  </si>
+  <si>
+    <t>DUR-DEC-005</t>
+  </si>
+  <si>
+    <t>Type decimal in Normal std field</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Normal" distribution
+4. Mean has a value, Std field is accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Std field
+2. Clear any existing value
+3. Type "0.25" character by character
+4. Watch the field during typing
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Field progressively shows: "0", "0.", "0.2", "0.25"
+2. Decimal is handled correctly in Std field
+3. After blur, Std shows "0.25"
+4. The value persists (doesn't reset)
+5. Note: Very small Std (like 0.1) is enforced minimum</t>
+  </si>
+  <si>
+    <t>DUR-DEC-006</t>
+  </si>
+  <si>
+    <t>Type decimal in Uniform low field</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Uniform" distribution
+4. Low and High fields are visible</t>
+  </si>
+  <si>
+    <t>1. Click inside the Low field
+2. Clear any existing value
+3. Type "0.1" character by character
+4. Watch the field during typing
+5. Press Tab to move to High field</t>
+  </si>
+  <si>
+    <t>1. Field progressively shows: "0", "0.", "0.1"
+2. Decimal is handled correctly in Low field
+3. After Tab, Low shows "0.1"
+4. The value persists when moving to High field
+5. Uniform distribution accepts decimal low values</t>
+  </si>
+  <si>
+    <t>DUR-DEC-007</t>
+  </si>
+  <si>
+    <t>Type decimal in Uniform high field</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Uniform" distribution
+4. Low has value "0.1", High field is accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside the High field
+2. Clear any existing value
+3. Type "2.5" character by character
+4. Watch the field during typing
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Field progressively shows: "2", "2.", "2.5"
+2. Decimal is handled correctly in High field
+3. After blur, High shows "2.5"
+4. Low field still shows its value (not erased)
+5. Both decimal values are maintained</t>
+  </si>
+  <si>
+    <t>DUR-DEC-008</t>
+  </si>
+  <si>
+    <t>Type decimals in all Triangular fields</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select "Triangular" distribution
+4. Left, Mode, Right fields are visible</t>
+  </si>
+  <si>
+    <t>1. Click Left, clear, type "0.5", blur
+2. Click Mode, clear, type "1.5", blur
+3. Click Right, clear, type "2.5", blur
+4. Watch each field during typing
+5. Verify all values after completing</t>
+  </si>
+  <si>
+    <t>1. Each field handles decimal input correctly
+2. Left shows "0.5", Mode shows "1.5", Right shows "2.5"
+3. No field resets or clears during typing
+4. All three decimal values persist
+5. Triangular constraints maintained: 0.5 &lt; 1.5 &lt; 2.5</t>
+  </si>
+  <si>
+    <t>DUR-DEC-009</t>
+  </si>
+  <si>
+    <t>Clear field and retype decimal</t>
+  </si>
+  <si>
+    <t>1. Have any distribution selected in Duration Editor
+2. A numeric field has a value (like "5")
+3. This tests clearing and re-entering decimals</t>
+  </si>
+  <si>
+    <t>1. Click inside the field with value "5"
+2. Select all (Ctrl+A) and delete to clear
+3. Field is now empty
+4. Type "0.75" character by character
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. After clearing, field shows empty or placeholder
+2. Typing "0.75" shows: "0", "0.", "0.7", "0.75"
+3. After blur, field shows "0.75"
+4. Clearing and retyping decimals works correctly
+5. This tests the full edit cycle with decimals</t>
+  </si>
+  <si>
+    <t>DUR-DEC-010</t>
+  </si>
+  <si>
+    <t>Type very small decimal (leading zeros)</t>
+  </si>
+  <si>
+    <t>1. Have any distribution selected in Duration Editor
+2. A numeric field is accessible
+3. This tests decimals with multiple leading zeros</t>
+  </si>
+  <si>
+    <t>1. Click inside the field
+2. Clear any existing value
+3. Type "0.001" character by character
+4. Watch the field during typing
+5. Press Tab or click outside to blur</t>
+  </si>
+  <si>
+    <t>1. Field progressively shows: "0", "0.", "0.0", "0.00", "0.001"
+2. Very small decimals are accepted
+3. After blur, field shows "0.001"
+4. Leading zeros after decimal are preserved
+5. Note: Some fields may have a minimum (like 0.01)</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-001</t>
+  </si>
+  <si>
+    <t>Enter very large number</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with any distribution
+3. A numeric field is accessible</t>
+  </si>
+  <si>
+    <t>1. Click inside any numeric field (e.g., Scale, Value, Mean)
+2. Clear any existing value
+3. Type "999999999" (nine 9s - very large number)
+4. Press Tab or click outside to blur
+5. Check if value is accepted</t>
+  </si>
+  <si>
+    <t>1. The field should either:
+   - Accept the large value and display it
+   - Enforce a maximum and adjust downward
+2. The application should NOT crash or freeze
+3. No JavaScript errors in console
+4. Note the actual behavior for the test result
+5. Large values may cause simulation issues but shouldn't break the UI</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-002</t>
+  </si>
+  <si>
+    <t>Enter very small decimal (0.0001)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with any distribution
+3. A numeric field is accessible (e.g., Exponential Scale)</t>
+  </si>
+  <si>
+    <t>1. Click inside the numeric field
+2. Clear any existing value
+3. Type "0.0001" (four decimal places)
+4. Press Tab or click outside to blur
+5. Check how the value is displayed</t>
+  </si>
+  <si>
+    <t>1. The field should accept very small decimals
+2. Display may show "0.0001" or scientific notation
+3. Some fields may enforce a minimum (like 0.01)
+4. The application should handle gracefully
+5. Note the actual precision supported</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-003</t>
+  </si>
+  <si>
+    <t>Enter many decimal places (1.123456789)</t>
+  </si>
+  <si>
+    <t>1. Click inside the numeric field
+2. Clear any existing value
+3. Type "1.123456789" (9 decimal places)
+4. Press Tab or click outside to blur
+5. Check how the value is displayed</t>
+  </si>
+  <si>
+    <t>1. The field should handle many decimal places
+2. Value may be:
+   - Accepted as-is: "1.123456789"
+   - Rounded: "1.12" or "1.123"
+   - Truncated to fixed precision
+3. No errors should occur
+4. Note the actual precision used
+5. Very high precision may not affect simulation</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-004</t>
+  </si>
+  <si>
+    <t>Rapid focus/blur cycling (10 times)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with any distribution
+3. A numeric field has a value (e.g., "5")</t>
+  </si>
+  <si>
+    <t>1. Click inside the field (focus)
+2. Immediately click outside (blur)
+3. Repeat steps 1-2 rapidly 10 times
+4. After 10 cycles, check the field value
+5. Check for any errors in browser console</t>
+  </si>
+  <si>
+    <t>1. The field value should remain stable (still "5")
+2. No flickering or display glitches
+3. No JavaScript errors in browser console
+4. The application handles rapid focus/blur gracefully
+5. No race conditions or state corruption</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-005</t>
+  </si>
+  <si>
+    <t>Keyboard Tab navigation through all fields</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. Select a distribution with multiple fields (e.g., Normal or Triangular)</t>
+  </si>
+  <si>
+    <t>1. Click on the distribution dropdown to focus
+2. Press Tab to move to first numeric field
+3. Press Tab again to move to second field
+4. Continue pressing Tab through all fields
+5. Observe the focus order and field highlighting</t>
+  </si>
+  <si>
+    <t>1. Tab should move focus in logical order:
+   - Dropdown → First field → Second field → etc.
+2. Each focused field should be visually highlighted
+3. No fields should be skipped
+4. Focus should eventually leave the Duration Editor
+5. Tab navigation provides keyboard accessibility</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-006</t>
+  </si>
+  <si>
+    <t>Arrow keys increment/decrement value</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with any distribution
+3. A numeric field is focused (clicked inside)</t>
+  </si>
+  <si>
+    <t>1. Click inside a numeric field (e.g., Scale=5)
+2. Press the UP arrow key on keyboard
+3. Observe the value change
+4. Press the DOWN arrow key
+5. Observe the value change</t>
+  </si>
+  <si>
+    <t>1. UP arrow should increase the value (5 → 5.01 or 6)
+2. DOWN arrow should decrease the value (back toward 5)
+3. The step amount matches the spinner arrows
+4. Arrow keys provide keyboard alternative to spinner
+5. Minimum/maximum values should be enforced</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-007</t>
+  </si>
+  <si>
+    <t>Paste invalid text (abc)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible with any distribution
+3. A numeric field is accessible
+4. Copy the text "abc" to clipboard</t>
+  </si>
+  <si>
+    <t>1. Click inside the numeric field
+2. Clear any existing value
+3. Paste "abc" from clipboard (Ctrl+V)
+4. Press Tab or click outside to blur
+5. Watch what happens to the invalid input</t>
+  </si>
+  <si>
+    <t>1. The field should reject the non-numeric text
+2. Possible behaviors:
+   - Field clears or shows empty
+   - Field reverts to previous valid value
+   - Field shows 0 or default
+3. No JavaScript errors should occur
+4. Invalid input is handled gracefully
+5. Note the actual behavior for test result</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-008</t>
+  </si>
+  <si>
+    <t>Enter scientific notation (1e5 or 1E-3)</t>
+  </si>
+  <si>
+    <t>1. Click inside the numeric field
+2. Clear any existing value
+3. Type "1e5" (scientific notation for 100000)
+4. Press Tab or click outside to blur
+5. Alternatively try "1E-3" (0.001)</t>
+  </si>
+  <si>
+    <t>1. Check how scientific notation is handled:
+   - May convert "1e5" to "100000"
+   - May reject and revert to previous value
+   - May show an error
+2. The behavior should be consistent
+3. No crashes or freezes
+4. Note the actual handling for test result
+5. Scientific notation is valid in JavaScript</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-009</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Switch distribution types rapidly (5 times)</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor is visible
+3. The distribution dropdown is accessible</t>
+  </si>
+  <si>
+    <t>1. Click the distribution type dropdown
+2. Select "Exponential", wait 1 second
+3. Open dropdown, select "Normal"
+4. Open dropdown, select "Uniform"
+5. Continue switching 5 times rapidly
+6. End on a specific type and check fields</t>
+  </si>
+  <si>
+    <t>1. Each distribution change should show correct fields
+2. No visual glitches during rapid switching
+3. Final state shows correct fields for selected type
+4. No JavaScript errors in browser console
+5. The editor handles rapid type changes gracefully</t>
+  </si>
+  <si>
+    <t>DUR-EDGE-010</t>
+  </si>
+  <si>
+    <t>Edit one field immediately after another</t>
+  </si>
+  <si>
+    <t>1. Have an Activity or Generator selected
+2. Duration Editor visible with multi-field distribution
+3. Select Normal (Mean + Std) or Uniform (Low + High)</t>
+  </si>
+  <si>
+    <t>1. Click Mean field, type "10" (don't blur yet)
+2. Immediately click Std field (this blurs Mean)
+3. Type "2" in Std
+4. Immediately click Mean field again
+5. Check both field values</t>
+  </si>
+  <si>
+    <t>1. Mean should show "10" after first blur
+2. Std should show "2" after being edited
+3. Both values should persist correctly
+4. Rapid field switching doesn't cause value loss
+5. This tests immediate sequential editing</t>
   </si>
 </sst>
 </file>
@@ -214,7 +1850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
@@ -224,6 +1860,9 @@
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -595,107 +2234,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-EXP-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Enter valid scale value</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter 1.5 in scale field</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Value updates to 1.5, Save enables</t>
-        </is>
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -707,35 +2334,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-EXP-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Enter decimal like 0.25</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Type 0.25 in scale field</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Value updates to 0.25</t>
-        </is>
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -747,35 +2362,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-EXP-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Enter value below minimum</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Enter 0 in scale field, blur</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Value enforces minimum (0.01)</t>
-        </is>
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -787,35 +2390,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-EXP-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Clear field and blur</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Exponential with value</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Clear scale field, blur</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -827,35 +2418,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-EXP-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Use spinner increase</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Exponential with scale=1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Click up arrow on scale</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Scale increases by step amount</t>
-        </is>
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -867,35 +2446,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-EXP-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Use spinner decrease</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Exponential with scale=1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Click down arrow on scale</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Scale decreases (min 0.01)</t>
-        </is>
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -907,35 +2474,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-EXP-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Enter negative value</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Enter -1 in scale field, blur</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Value enforces minimum (0.01)</t>
-        </is>
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -947,35 +2502,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-EXP-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Enter very large value</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Enter 10000 in scale field</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Value updates to 10000</t>
-        </is>
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -1001,107 +2544,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-CONST-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Enter positive value</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Constant distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter 10 in value field</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Value updates to 10, Save enables</t>
-        </is>
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" t="s">
+        <v>91</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -1113,35 +2644,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-CONST-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Enter zero</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Constant distribution selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Enter 0 in value field</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Value updates to 0</t>
-        </is>
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>96</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -1153,35 +2672,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-CONST-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Enter negative value</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Constant distribution selected</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Enter -5 in value field</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Value updates to -5 (if allowed)</t>
-        </is>
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -1193,35 +2700,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-CONST-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Enter decimal value</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Constant distribution selected</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Enter 2.5 in value field</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Value updates to 2.5</t>
-        </is>
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" t="s">
+        <v>105</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -1233,35 +2728,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-CONST-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Clear field and blur</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Constant with value</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Clear value field, blur</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" t="s">
+        <v>109</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -1273,35 +2756,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-CONST-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Use spinner controls</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Constant with value=5</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Click up/down arrows</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Value increases/decreases by step</t>
-        </is>
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" t="s">
+        <v>114</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -1327,107 +2798,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-NORM-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Enter valid mean</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter 10 in mean field</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Value updates to 10, Save enables</t>
-        </is>
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" t="s">
+        <v>119</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -1439,35 +2898,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-NORM-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Enter valid std</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Enter 2 in std field</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Value updates to 2</t>
-        </is>
+      <c r="A3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
+        <v>124</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -1479,35 +2926,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-NORM-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Enter negative mean</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Enter -5 in mean field</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Value updates to -5 (mean can be negative)</t>
-        </is>
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>129</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -1519,35 +2954,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-NORM-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Enter zero std</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Enter 0 in std field, blur</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Value enforces minimum (0.1)</t>
-        </is>
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" t="s">
+        <v>134</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -1559,35 +2982,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-NORM-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Enter negative std</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Enter -1 in std field, blur</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Value enforces minimum (0.1)</t>
-        </is>
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" t="s">
+        <v>139</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -1599,35 +3010,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-NORM-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Clear mean field</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Normal with mean=10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Clear mean field, blur</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" t="s">
+        <v>144</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -1639,35 +3038,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-NORM-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Clear std field</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Normal with std=2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Clear std field, blur</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" t="s">
+        <v>149</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -1679,35 +3066,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-NORM-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Enter decimal mean and std</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Enter 5.5 mean, 1.25 std</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Both values update correctly</t>
-        </is>
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" t="s">
+        <v>154</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -1726,16 +3101,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -1773,13 +3148,13 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
@@ -1814,16 +3189,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
@@ -1865,107 +3240,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-UNI-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Enter valid low and high</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Uniform distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter low=5, high=15</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Both values update, Save enables</t>
-        </is>
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" t="s">
+        <v>170</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -1977,35 +3340,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-UNI-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Set low equal to high</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Uniform with low=5, high=15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Set low=15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>High auto-adjusts to low+0.01</t>
-        </is>
+      <c r="A3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" t="s">
+        <v>175</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2017,35 +3368,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-UNI-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Set low greater than high</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Uniform with low=5, high=15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Set low=20</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>High auto-adjusts to 20.01</t>
-        </is>
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2057,35 +3396,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-UNI-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Set high equal to low</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Uniform with low=5, high=15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Set high=5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Low auto-adjusts to high-0.01</t>
-        </is>
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>183</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2097,35 +3424,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-UNI-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Set high less than low</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Uniform with low=5, high=15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Set high=2</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Low auto-adjusts to 1.99</t>
-        </is>
+      <c r="A6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" t="s">
+        <v>187</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2137,35 +3452,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-UNI-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Enter decimal values</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Uniform distribution selected</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Enter low=0.5, high=2.75</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Both decimal values update</t>
-        </is>
+      <c r="A7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" t="s">
+        <v>192</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -2177,35 +3480,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-UNI-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Clear low field</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Uniform with values</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Clear low field, blur</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" t="s">
+        <v>197</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -2217,35 +3508,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-UNI-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Clear high field</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Uniform with values</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Clear high field, blur</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" t="s">
+        <v>201</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -2264,16 +3543,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -2311,13 +3590,13 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>206</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
@@ -2355,13 +3634,13 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
@@ -2403,107 +3682,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-TRI-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Enter valid left/mode/right</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Triangular distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter left=1, mode=5, right=10</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>All values update, Save enables</t>
-        </is>
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" t="s">
+        <v>213</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2515,35 +3782,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-TRI-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Set left greater than mode</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Triangular with left=1, mode=5, right=10</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Set left=7</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mode and right cascade adjust</t>
-        </is>
+      <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3" t="s">
+        <v>218</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2555,35 +3810,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-TRI-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Set right less than mode</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Triangular with left=1, mode=5, right=10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Set right=3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mode and left cascade adjust</t>
-        </is>
+      <c r="A4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F4" t="s">
+        <v>222</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2595,35 +3838,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-TRI-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Set mode below left</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Triangular with left=1, mode=5, right=10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Set mode=0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Left adjusts to mode-0.01</t>
-        </is>
+      <c r="A5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
+        <v>226</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2635,35 +3866,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-TRI-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Set mode above right</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Triangular with left=1, mode=5, right=10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Set mode=15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Right adjusts to mode+0.01</t>
-        </is>
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" t="s">
+        <v>230</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2675,35 +3894,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-TRI-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Enter decimal values</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Triangular distribution selected</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Enter left=0.5, mode=1.75, right=3.25</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>All decimal values update</t>
-        </is>
+      <c r="A7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" t="s">
+        <v>235</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -2715,35 +3922,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-TRI-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Set all three equal</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Triangular distribution selected</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Try to set left=mode=right=5</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Enforces minimum spread</t>
-        </is>
+      <c r="A8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" t="s">
+        <v>240</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -2755,35 +3950,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-TRI-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Clear left field</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Triangular with values</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Clear left field, blur</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" t="s">
+        <v>244</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -2795,35 +3978,23 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DUR-TRI-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Clear mode field</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Triangular with values</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Clear mode field, blur</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" t="s">
+        <v>248</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -2835,35 +4006,23 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DUR-TRI-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Clear right field</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Triangular with values</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Clear right field, blur</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Reverts to previous valid value</t>
-        </is>
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" t="s">
+        <v>252</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -2882,16 +4041,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>3</v>
+        <v>253</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>254</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>255</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
@@ -2929,13 +4088,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>256</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="G13" t="s">
         <v>6</v>
@@ -2973,13 +4132,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="G14" t="s">
         <v>6</v>
@@ -3021,107 +4180,95 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-DEC-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Type .25 in scale field</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Type .25 (starting with dot)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Value shows .25 or 0.25</t>
-        </is>
+      <c r="A2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F2" t="s">
+        <v>264</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3137,35 +4284,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-DEC-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Type 0.25 in scale field</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Type 0.25 character by character</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Value updates smoothly to 0.25</t>
-        </is>
+      <c r="A3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" t="s">
+        <v>269</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3177,35 +4312,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-DEC-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Type 0. then 2 then 5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Exponential distribution selected</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Type 0, then ., then 2, then 5</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Field shows 0., 0.2, 0.25 progressively</t>
-        </is>
+      <c r="A4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F4" t="s">
+        <v>274</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3221,35 +4344,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-DEC-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Type decimal in mean field</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Type 0.5 in mean field</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Value updates to 0.5</t>
-        </is>
+      <c r="A5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" t="s">
+        <v>279</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3261,35 +4372,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-DEC-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Type decimal in std field</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Normal distribution selected</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Type 0.25 in std field</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Value updates to 0.25</t>
-        </is>
+      <c r="A6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" t="s">
+        <v>284</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3301,35 +4400,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-DEC-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Type decimal in low field</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Uniform distribution selected</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Type 0.1 in low field</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Value updates to 0.1</t>
-        </is>
+      <c r="A7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" t="s">
+        <v>289</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3341,35 +4428,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-DEC-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Type decimal in high field</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Uniform distribution selected</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Type 2.5 in high field</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Value updates to 2.5</t>
-        </is>
+      <c r="A8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" t="s">
+        <v>294</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3381,35 +4456,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-DEC-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Type decimal in triangular fields</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Triangular distribution selected</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Type 0.5 in left, 1.5 in mode, 2.5 in right</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>All values update correctly</t>
-        </is>
+      <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" t="s">
+        <v>299</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3421,35 +4484,23 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DUR-DEC-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Clear and retype decimal</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Any distribution with value</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Clear field, type new decimal 0.75</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>New decimal value accepted</t>
-        </is>
+      <c r="A10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" t="s">
+        <v>304</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3461,35 +4512,23 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DUR-DEC-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Type leading zero decimal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Type 0.001</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Very small decimal accepted</t>
-        </is>
+      <c r="A11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D11" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" t="s">
+        <v>309</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -3530,107 +4569,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Steps to Reproduce</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Date Tested</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Build/Version</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Bug Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Very large numbers</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Enter 999999999 in value field</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Value accepted or max enforced</t>
-        </is>
+      <c r="A2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" t="s">
+        <v>314</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3642,35 +4669,23 @@
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Very small decimals</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Enter 0.0001 in value field</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Small decimal accepted</t>
-        </is>
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" t="s">
+        <v>319</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3682,35 +4697,23 @@
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Many decimal places</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Enter 1.123456789</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Value rounded or truncated appropriately</t>
-        </is>
+      <c r="A4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F4" t="s">
+        <v>323</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3722,35 +4725,23 @@
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Rapid focus/blur cycling</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Click in/out of field rapidly 10 times</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No errors, value stable</t>
-        </is>
+      <c r="A5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E5" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" t="s">
+        <v>328</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3762,35 +4753,23 @@
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Keyboard navigation</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Distribution type dropdown</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Tab through all fields</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Focus moves correctly through all inputs</t>
-        </is>
+      <c r="A6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F6" t="s">
+        <v>333</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3802,35 +4781,23 @@
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Arrow keys in number field</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Any numeric field focused</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Press up/down arrow keys</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Value increments/decrements by step</t>
-        </is>
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F7" t="s">
+        <v>338</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3842,35 +4809,23 @@
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Paste invalid value</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Any numeric field</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Paste text abc into field</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Invalid input rejected or cleared</t>
-        </is>
+      <c r="A8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E8" t="s">
+        <v>342</v>
+      </c>
+      <c r="F8" t="s">
+        <v>343</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3882,35 +4837,23 @@
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Scientific notation input</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Any distribution</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Type 1e5 or 1E-3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Scientific notation handled appropriately</t>
-        </is>
+      <c r="A9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F9" t="s">
+        <v>347</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3922,35 +4865,23 @@
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Switch distribution types rapidly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Editor open</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Change distribution type 5 times quickly</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>No errors, final type displays correctly</t>
-        </is>
+      <c r="A10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" t="s">
+        <v>351</v>
+      </c>
+      <c r="E10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" t="s">
+        <v>353</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3962,35 +4893,23 @@
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DUR-EDGE-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Multiple fields simultaneous edit</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Normal/Uniform/Triangular</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Edit one field, immediately edit another</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Both values update correctly</t>
-        </is>
+      <c r="A11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F11" t="s">
+        <v>358</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
